--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/01 18:43:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-10</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 18:43:40</t>
+          <t>07/03 20:48:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -110,7 +110,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,32 +75,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -110,7 +110,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/15 14:58:05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1335.31</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/15 14:41:32</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>6.74</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1261.13</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2596.44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1261.13</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2596.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/15 14:58:05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1335.31</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/15 14:41:32</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6.74</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1261.13</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2596.44</t>
+          <t>30000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3931.75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2596.44</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3931.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -72,186 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>07/25 11:52:03</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2413.96</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>322.34</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>322.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/25 11:52:39</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2413.96</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>358.69</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2413.96</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358.69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>358.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/25 11:52:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3030.91</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/25 11:52:39</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>358.69</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2413.96</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>22811.96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3389.59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>358.69</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3389.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/25 11:52:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3030.91</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/25 11:52:39</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>358.69</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22811.96</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3389.59</t>
+          <t>23811.96</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3514.59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3389.59</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3514.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 12:23:13</t>
+          <t>07/25 12:23:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/25 11:52:52</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3030.91</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/25 11:52:39</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>358.69</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>23811.96</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3514.59</t>
+          <t>44209.96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5928.56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3514.59</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5928.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 12:23:21</t>
+          <t>07/25 12:24:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 12:23:13</t>
+          <t>07/25 12:23:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,183 +201,225 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/25 11:52:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.73</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3030.91</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/25 11:52:39</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>358.69</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>44209.96</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5928.56</t>
+          <t>64607.96</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8273.16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5928.56</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8273.16</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/25 13:06:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2344.6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20398</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2344.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/25 13:07:15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2413.96</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/25 13:06:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2344.6</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>20398</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>40796</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4758.56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2344.6</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4758.56</t>
         </is>
       </c>
     </row>
